--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\gx_pit_mom_Auto_Bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B4B22C2-AE99-481A-A6D2-89898E9BC928}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F54E897-3A86-4F4F-B0CA-9E05FDBB98BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="-8710" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="file" sheetId="1" r:id="rId1"/>
@@ -204,7 +204,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -221,13 +221,10 @@
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -565,7 +562,7 @@
     <col min="1" max="2" width="10.6328125" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="9.81640625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.453125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.36328125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.25">
@@ -588,7 +585,7 @@
       <c r="A3" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="3" t="s">
         <v>6</v>
       </c>
     </row>
@@ -602,22 +599,22 @@
       </c>
     </row>
     <row r="5" spans="1:7" ht="25" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="7" t="s">
         <v>14</v>
       </c>
       <c r="G5" s="4" t="s">
@@ -628,19 +625,19 @@
       <c r="A6" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="7" t="s">
+      <c r="E6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="3" t="s">
         <v>19</v>
       </c>
       <c r="G6" s="3" t="s">
@@ -7619,13 +7616,21 @@
       <c r="A310" s="1">
         <v>46120</v>
       </c>
-      <c r="B310" s="5"/>
-      <c r="C310" s="5"/>
-      <c r="D310" s="5"/>
+      <c r="B310" s="5">
+        <v>5933.5302000000001</v>
+      </c>
+      <c r="C310" s="5">
+        <v>6059.7473</v>
+      </c>
+      <c r="D310" s="5">
+        <v>5933.1761999999999</v>
+      </c>
       <c r="E310" s="5">
-        <v>5822.7453999999998</v>
-      </c>
-      <c r="F310" s="5"/>
+        <v>6059.7473</v>
+      </c>
+      <c r="F310" s="5">
+        <v>136584686300</v>
+      </c>
       <c r="G310" s="5"/>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\gx_pit_mom_Auto_Bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F54E897-3A86-4F4F-B0CA-9E05FDBB98BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE917773-05E5-4D37-9376-659D82F18D90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-8710" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2200" yWindow="2200" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="file" sheetId="1" r:id="rId1"/>
@@ -649,7 +649,7 @@
         <v>45659</v>
       </c>
       <c r="B7" s="5">
-        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=304")</f>
+        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=306")</f>
         <v>4744.6453000000001</v>
       </c>
       <c r="C7" s="5">
@@ -7629,26 +7629,50 @@
         <v>6059.7473</v>
       </c>
       <c r="F310" s="5">
-        <v>136584686300</v>
+        <v>136584686390.00002</v>
       </c>
       <c r="G310" s="5"/>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A311" s="1"/>
-      <c r="B311" s="5"/>
-      <c r="C311" s="5"/>
-      <c r="D311" s="5"/>
-      <c r="E311" s="5"/>
-      <c r="F311" s="5"/>
+      <c r="A311" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B311" s="5">
+        <v>6010.241</v>
+      </c>
+      <c r="C311" s="5">
+        <v>6043.8197</v>
+      </c>
+      <c r="D311" s="5">
+        <v>5998.6279000000004</v>
+      </c>
+      <c r="E311" s="5">
+        <v>6020.0529999999999</v>
+      </c>
+      <c r="F311" s="5">
+        <v>117095363438.00002</v>
+      </c>
       <c r="G311" s="5"/>
     </row>
     <row r="312" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A312" s="1"/>
-      <c r="B312" s="5"/>
-      <c r="C312" s="5"/>
-      <c r="D312" s="5"/>
-      <c r="E312" s="5"/>
-      <c r="F312" s="5"/>
+      <c r="A312" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B312" s="5">
+        <v>6060.5748000000003</v>
+      </c>
+      <c r="C312" s="5">
+        <v>6127.2728999999999</v>
+      </c>
+      <c r="D312" s="5">
+        <v>6056.9373999999998</v>
+      </c>
+      <c r="E312" s="5">
+        <v>6090.0618999999997</v>
+      </c>
+      <c r="F312" s="5">
+        <v>118993565900</v>
+      </c>
       <c r="G312" s="5"/>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\gx_pit_mom_Auto_Bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE917773-05E5-4D37-9376-659D82F18D90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F54D78D1-882C-477B-A317-2EB0E85C88BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2200" yWindow="2200" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25490" yWindow="-8710" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="file" sheetId="1" r:id="rId1"/>
@@ -649,7 +649,7 @@
         <v>45659</v>
       </c>
       <c r="B7" s="5">
-        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=306")</f>
+        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=307")</f>
         <v>4744.6453000000001</v>
       </c>
       <c r="C7" s="5">
@@ -7671,17 +7671,29 @@
         <v>6090.0618999999997</v>
       </c>
       <c r="F312" s="5">
-        <v>118993565900</v>
+        <v>118993565974</v>
       </c>
       <c r="G312" s="5"/>
     </row>
     <row r="313" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A313" s="1"/>
-      <c r="B313" s="5"/>
-      <c r="C313" s="5"/>
-      <c r="D313" s="5"/>
-      <c r="E313" s="5"/>
-      <c r="F313" s="5"/>
+      <c r="A313" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B313" s="5">
+        <v>6057.9394000000002</v>
+      </c>
+      <c r="C313" s="5">
+        <v>6112.2728999999999</v>
+      </c>
+      <c r="D313" s="5">
+        <v>6057.9394000000002</v>
+      </c>
+      <c r="E313" s="5">
+        <v>6103.8424000000005</v>
+      </c>
+      <c r="F313" s="5">
+        <v>114027966000</v>
+      </c>
       <c r="G313" s="5"/>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\gx_pit_mom_Auto_Bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F54D78D1-882C-477B-A317-2EB0E85C88BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E07CFC7-AA95-4110-BA3F-1DB1E6126AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25490" yWindow="-8710" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -649,7 +649,7 @@
         <v>45659</v>
       </c>
       <c r="B7" s="5">
-        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=307")</f>
+        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=308")</f>
         <v>4744.6453000000001</v>
       </c>
       <c r="C7" s="5">
@@ -7692,17 +7692,29 @@
         <v>6103.8424000000005</v>
       </c>
       <c r="F313" s="5">
-        <v>114027966000</v>
+        <v>114027966094</v>
       </c>
       <c r="G313" s="5"/>
     </row>
     <row r="314" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A314" s="1"/>
-      <c r="B314" s="5"/>
-      <c r="C314" s="5"/>
-      <c r="D314" s="5"/>
-      <c r="E314" s="5"/>
-      <c r="F314" s="5"/>
+      <c r="A314" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B314" s="5">
+        <v>6146.4192999999996</v>
+      </c>
+      <c r="C314" s="5">
+        <v>6181.4331000000002</v>
+      </c>
+      <c r="D314" s="5">
+        <v>6116.8975</v>
+      </c>
+      <c r="E314" s="5">
+        <v>6181.433</v>
+      </c>
+      <c r="F314" s="5">
+        <v>122036722000</v>
+      </c>
       <c r="G314" s="5"/>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\gx_pit_mom_Auto_Bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E07CFC7-AA95-4110-BA3F-1DB1E6126AF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28FF6D56-4B54-4D69-A523-07440FF3C7B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25490" yWindow="-8710" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -649,7 +649,7 @@
         <v>45659</v>
       </c>
       <c r="B7" s="5">
-        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=308")</f>
+        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=309")</f>
         <v>4744.6453000000001</v>
       </c>
       <c r="C7" s="5">
@@ -7713,17 +7713,29 @@
         <v>6181.433</v>
       </c>
       <c r="F314" s="5">
-        <v>122036722000</v>
+        <v>122036722086.99998</v>
       </c>
       <c r="G314" s="5"/>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A315" s="1"/>
-      <c r="B315" s="5"/>
-      <c r="C315" s="5"/>
-      <c r="D315" s="5"/>
-      <c r="E315" s="5"/>
-      <c r="F315" s="5"/>
+      <c r="A315" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B315" s="5">
+        <v>6213.9530000000004</v>
+      </c>
+      <c r="C315" s="5">
+        <v>6215.4341999999997</v>
+      </c>
+      <c r="D315" s="5">
+        <v>6137.4387999999999</v>
+      </c>
+      <c r="E315" s="5">
+        <v>6153.9589999999998</v>
+      </c>
+      <c r="F315" s="5">
+        <v>123465803600</v>
+      </c>
       <c r="G315" s="5"/>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\gx_pit_mom_Auto_Bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28FF6D56-4B54-4D69-A523-07440FF3C7B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E773BBC6-71EC-4BEB-A660-1E153E1AEC55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25490" yWindow="-8710" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="26700" yWindow="-7500" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="file" sheetId="1" r:id="rId1"/>
@@ -649,7 +649,7 @@
         <v>45659</v>
       </c>
       <c r="B7" s="5">
-        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=309")</f>
+        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=310")</f>
         <v>4744.6453000000001</v>
       </c>
       <c r="C7" s="5">
@@ -7734,17 +7734,29 @@
         <v>6153.9589999999998</v>
       </c>
       <c r="F315" s="5">
-        <v>123465803600</v>
+        <v>123465803620</v>
       </c>
       <c r="G315" s="5"/>
     </row>
     <row r="316" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A316" s="1"/>
-      <c r="B316" s="5"/>
-      <c r="C316" s="5"/>
-      <c r="D316" s="5"/>
-      <c r="E316" s="5"/>
-      <c r="F316" s="5"/>
+      <c r="A316" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B316" s="5">
+        <v>6165.4845999999998</v>
+      </c>
+      <c r="C316" s="5">
+        <v>6243.183</v>
+      </c>
+      <c r="D316" s="5">
+        <v>6158.2856000000002</v>
+      </c>
+      <c r="E316" s="5">
+        <v>6239.4853000000003</v>
+      </c>
+      <c r="F316" s="5">
+        <v>120104439900</v>
+      </c>
       <c r="G316" s="5"/>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\gx_pit_mom_Auto_Bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E773BBC6-71EC-4BEB-A660-1E153E1AEC55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF94C56D-9DC8-47D6-A414-BF28D1F721CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="26700" yWindow="-7500" windowWidth="14400" windowHeight="7270" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="file" sheetId="1" r:id="rId1"/>
@@ -649,7 +649,7 @@
         <v>45659</v>
       </c>
       <c r="B7" s="5">
-        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=310")</f>
+        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=312")</f>
         <v>4744.6453000000001</v>
       </c>
       <c r="C7" s="5">
@@ -7755,26 +7755,50 @@
         <v>6239.4853000000003</v>
       </c>
       <c r="F316" s="5">
-        <v>120104439900</v>
+        <v>120104439935.99998</v>
       </c>
       <c r="G316" s="5"/>
     </row>
     <row r="317" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A317" s="1"/>
-      <c r="B317" s="5"/>
-      <c r="C317" s="5"/>
-      <c r="D317" s="5"/>
-      <c r="E317" s="5"/>
-      <c r="F317" s="5"/>
+      <c r="A317" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B317" s="5">
+        <v>6227.7043999999996</v>
+      </c>
+      <c r="C317" s="5">
+        <v>6266.9029</v>
+      </c>
+      <c r="D317" s="5">
+        <v>6217.6391000000003</v>
+      </c>
+      <c r="E317" s="5">
+        <v>6254.1136999999999</v>
+      </c>
+      <c r="F317" s="5">
+        <v>121887734911.99998</v>
+      </c>
       <c r="G317" s="5"/>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A318" s="1"/>
-      <c r="B318" s="5"/>
-      <c r="C318" s="5"/>
-      <c r="D318" s="5"/>
-      <c r="E318" s="5"/>
-      <c r="F318" s="5"/>
+      <c r="A318" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B318" s="5">
+        <v>6254.8501999999999</v>
+      </c>
+      <c r="C318" s="5">
+        <v>6305.7151000000003</v>
+      </c>
+      <c r="D318" s="5">
+        <v>6250.4829</v>
+      </c>
+      <c r="E318" s="5">
+        <v>6300.2141000000001</v>
+      </c>
+      <c r="F318" s="5">
+        <v>128935679000</v>
+      </c>
       <c r="G318" s="5"/>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\gx_pit_mom_Auto_Bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF94C56D-9DC8-47D6-A414-BF28D1F721CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64DB95C1-14DE-4458-AE96-E0500E74EC06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1900" yWindow="1900" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="file" sheetId="1" r:id="rId1"/>
@@ -649,7 +649,7 @@
         <v>45659</v>
       </c>
       <c r="B7" s="5">
-        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=312")</f>
+        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=313")</f>
         <v>4744.6453000000001</v>
       </c>
       <c r="C7" s="5">
@@ -7797,17 +7797,29 @@
         <v>6300.2141000000001</v>
       </c>
       <c r="F318" s="5">
-        <v>128935679000</v>
+        <v>128935679011.99998</v>
       </c>
       <c r="G318" s="5"/>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A319" s="1"/>
-      <c r="B319" s="5"/>
-      <c r="C319" s="5"/>
-      <c r="D319" s="5"/>
-      <c r="E319" s="5"/>
-      <c r="F319" s="5"/>
+      <c r="A319" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B319" s="5">
+        <v>6285.1337000000003</v>
+      </c>
+      <c r="C319" s="5">
+        <v>6303.1450000000004</v>
+      </c>
+      <c r="D319" s="5">
+        <v>6240.6715999999997</v>
+      </c>
+      <c r="E319" s="5">
+        <v>6297.9135999999999</v>
+      </c>
+      <c r="F319" s="5">
+        <v>124820769435.99998</v>
+      </c>
       <c r="G319" s="5"/>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\gx_pit_mom_Auto_Bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{64DB95C1-14DE-4458-AE96-E0500E74EC06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{049A1E35-AF98-4900-AF2C-AC280A567BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1900" yWindow="1900" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -649,7 +649,7 @@
         <v>45659</v>
       </c>
       <c r="B7" s="5">
-        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=313")</f>
+        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=314")</f>
         <v>4744.6453000000001</v>
       </c>
       <c r="C7" s="5">
@@ -7823,12 +7823,24 @@
       <c r="G319" s="5"/>
     </row>
     <row r="320" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A320" s="1"/>
-      <c r="B320" s="5"/>
-      <c r="C320" s="5"/>
-      <c r="D320" s="5"/>
-      <c r="E320" s="5"/>
-      <c r="F320" s="5"/>
+      <c r="A320" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B320" s="5">
+        <v>6271.8168999999998</v>
+      </c>
+      <c r="C320" s="5">
+        <v>6358.2130999999999</v>
+      </c>
+      <c r="D320" s="5">
+        <v>6271.8168999999998</v>
+      </c>
+      <c r="E320" s="5">
+        <v>6357.0963000000002</v>
+      </c>
+      <c r="F320" s="5">
+        <v>125441681800</v>
+      </c>
       <c r="G320" s="5"/>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\gx_pit_mom_Auto_Bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{049A1E35-AF98-4900-AF2C-AC280A567BD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5909FDC7-9A86-43E7-BB91-152610F8D651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1900" yWindow="1900" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2240" yWindow="2240" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="file" sheetId="1" r:id="rId1"/>
@@ -649,7 +649,7 @@
         <v>45659</v>
       </c>
       <c r="B7" s="5">
-        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=314")</f>
+        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=316")</f>
         <v>4744.6453000000001</v>
       </c>
       <c r="C7" s="5">
@@ -7839,25 +7839,41 @@
         <v>6357.0963000000002</v>
       </c>
       <c r="F320" s="5">
-        <v>125441681800</v>
+        <v>125441681818</v>
       </c>
       <c r="G320" s="5"/>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A321" s="1"/>
-      <c r="B321" s="5"/>
-      <c r="C321" s="5"/>
-      <c r="D321" s="5"/>
-      <c r="E321" s="5"/>
-      <c r="F321" s="5"/>
+      <c r="A321" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B321" s="5">
+        <v>6368.9183000000003</v>
+      </c>
+      <c r="C321" s="5">
+        <v>6373.8748999999998</v>
+      </c>
+      <c r="D321" s="5">
+        <v>6263.8644000000004</v>
+      </c>
+      <c r="E321" s="5">
+        <v>6303.1041999999998</v>
+      </c>
+      <c r="F321" s="5">
+        <v>140367997980</v>
+      </c>
       <c r="G321" s="5"/>
     </row>
     <row r="322" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A322" s="1"/>
+      <c r="A322" s="1">
+        <v>46136</v>
+      </c>
       <c r="B322" s="5"/>
       <c r="C322" s="5"/>
       <c r="D322" s="5"/>
-      <c r="E322" s="5"/>
+      <c r="E322" s="5">
+        <v>6303.1041999999998</v>
+      </c>
       <c r="F322" s="5"/>
       <c r="G322" s="5"/>
     </row>

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\gx_pit_mom_Auto_Bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5909FDC7-9A86-43E7-BB91-152610F8D651}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D62CE0-ACDB-4C72-9542-D4F4A623C0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2240" yWindow="2240" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2280" yWindow="2280" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="file" sheetId="1" r:id="rId1"/>
@@ -7868,13 +7868,21 @@
       <c r="A322" s="1">
         <v>46136</v>
       </c>
-      <c r="B322" s="5"/>
-      <c r="C322" s="5"/>
-      <c r="D322" s="5"/>
+      <c r="B322" s="5">
+        <v>6275.3882000000003</v>
+      </c>
+      <c r="C322" s="5">
+        <v>6302.1926000000003</v>
+      </c>
+      <c r="D322" s="5">
+        <v>6229.5964999999997</v>
+      </c>
       <c r="E322" s="5">
-        <v>6303.1041999999998</v>
-      </c>
-      <c r="F322" s="5"/>
+        <v>6271.1736000000001</v>
+      </c>
+      <c r="F322" s="5">
+        <v>128680298549</v>
+      </c>
       <c r="G322" s="5"/>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\gx_pit_mom_Auto_Bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26D62CE0-ACDB-4C72-9542-D4F4A623C0D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44AA1387-943E-47E1-8899-DF111DAF27EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2280" yWindow="2280" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2620" yWindow="2620" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="file" sheetId="1" r:id="rId1"/>
@@ -649,7 +649,7 @@
         <v>45659</v>
       </c>
       <c r="B7" s="5">
-        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=316")</f>
+        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=318")</f>
         <v>4744.6453000000001</v>
       </c>
       <c r="C7" s="5">
@@ -7886,21 +7886,45 @@
       <c r="G322" s="5"/>
     </row>
     <row r="323" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A323" s="1"/>
-      <c r="B323" s="5"/>
-      <c r="C323" s="5"/>
-      <c r="D323" s="5"/>
-      <c r="E323" s="5"/>
-      <c r="F323" s="5"/>
+      <c r="A323" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B323" s="5">
+        <v>6269.8382000000001</v>
+      </c>
+      <c r="C323" s="5">
+        <v>6311.2452000000003</v>
+      </c>
+      <c r="D323" s="5">
+        <v>6248.6842999999999</v>
+      </c>
+      <c r="E323" s="5">
+        <v>6296.4468999999999</v>
+      </c>
+      <c r="F323" s="5">
+        <v>126983309494</v>
+      </c>
       <c r="G323" s="5"/>
     </row>
     <row r="324" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A324" s="1"/>
-      <c r="B324" s="5"/>
-      <c r="C324" s="5"/>
-      <c r="D324" s="5"/>
-      <c r="E324" s="5"/>
-      <c r="F324" s="5"/>
+      <c r="A324" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B324" s="5">
+        <v>6275.9633999999996</v>
+      </c>
+      <c r="C324" s="5">
+        <v>6286.6427999999996</v>
+      </c>
+      <c r="D324" s="5">
+        <v>6224.2130999999999</v>
+      </c>
+      <c r="E324" s="5">
+        <v>6246.7070000000003</v>
+      </c>
+      <c r="F324" s="5">
+        <v>129372108500</v>
+      </c>
       <c r="G324" s="5"/>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\gx_pit_mom_Auto_Bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44AA1387-943E-47E1-8899-DF111DAF27EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2AB5521-D1C3-44FF-87BA-D7656BDD6EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2620" yWindow="2620" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3300" yWindow="3300" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="file" sheetId="1" r:id="rId1"/>
@@ -649,7 +649,7 @@
         <v>45659</v>
       </c>
       <c r="B7" s="5">
-        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=318")</f>
+        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=320")</f>
         <v>4744.6453000000001</v>
       </c>
       <c r="C7" s="5">
@@ -7923,17 +7923,29 @@
         <v>6246.7070000000003</v>
       </c>
       <c r="F324" s="5">
-        <v>129372108500</v>
+        <v>129372108533.99998</v>
       </c>
       <c r="G324" s="5"/>
     </row>
     <row r="325" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A325" s="1"/>
-      <c r="B325" s="5"/>
-      <c r="C325" s="5"/>
-      <c r="D325" s="5"/>
-      <c r="E325" s="5"/>
-      <c r="F325" s="5"/>
+      <c r="A325" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B325" s="5">
+        <v>6212.2820000000002</v>
+      </c>
+      <c r="C325" s="5">
+        <v>6337.9757</v>
+      </c>
+      <c r="D325" s="5">
+        <v>6212.0297</v>
+      </c>
+      <c r="E325" s="5">
+        <v>6328.3635999999997</v>
+      </c>
+      <c r="F325" s="5">
+        <v>132476455394</v>
+      </c>
       <c r="G325" s="5"/>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\gx_pit_mom_Auto_Bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2AB5521-D1C3-44FF-87BA-D7656BDD6EF4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F83F2565-E999-4D36-8581-8CFE87D54203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3300" yWindow="3300" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7949,12 +7949,24 @@
       <c r="G325" s="5"/>
     </row>
     <row r="326" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A326" s="1"/>
-      <c r="B326" s="5"/>
-      <c r="C326" s="5"/>
-      <c r="D326" s="5"/>
-      <c r="E326" s="5"/>
-      <c r="F326" s="5"/>
+      <c r="A326" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B326" s="5">
+        <v>6335.2022999999999</v>
+      </c>
+      <c r="C326" s="5">
+        <v>6355.8788999999997</v>
+      </c>
+      <c r="D326" s="5">
+        <v>6320.1079</v>
+      </c>
+      <c r="E326" s="5">
+        <v>6342.2636000000002</v>
+      </c>
+      <c r="F326" s="5">
+        <v>136377224278</v>
+      </c>
       <c r="G326" s="5"/>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\gx_pit_mom_Auto_Bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F83F2565-E999-4D36-8581-8CFE87D54203}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5BACAAC-86F8-404B-B411-443E91669CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3300" yWindow="3300" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="file" sheetId="1" r:id="rId1"/>
@@ -649,7 +649,7 @@
         <v>45659</v>
       </c>
       <c r="B7" s="5">
-        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=320")</f>
+        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=321")</f>
         <v>4744.6453000000001</v>
       </c>
       <c r="C7" s="5">
@@ -7970,12 +7970,24 @@
       <c r="G326" s="5"/>
     </row>
     <row r="327" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A327" s="1"/>
-      <c r="B327" s="5"/>
-      <c r="C327" s="5"/>
-      <c r="D327" s="5"/>
-      <c r="E327" s="5"/>
-      <c r="F327" s="5"/>
+      <c r="A327" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B327" s="5">
+        <v>6404.7515000000003</v>
+      </c>
+      <c r="C327" s="5">
+        <v>6485.8957</v>
+      </c>
+      <c r="D327" s="5">
+        <v>6400.5267000000003</v>
+      </c>
+      <c r="E327" s="5">
+        <v>6465.5982999999997</v>
+      </c>
+      <c r="F327" s="5">
+        <v>149525707100</v>
+      </c>
       <c r="G327" s="5"/>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\gx_pit_mom_Auto_Bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5BACAAC-86F8-404B-B411-443E91669CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EE44C23-87BB-4A54-899C-F85B67989259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -649,7 +649,7 @@
         <v>45659</v>
       </c>
       <c r="B7" s="5">
-        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=321")</f>
+        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=325")</f>
         <v>4744.6453000000001</v>
       </c>
       <c r="C7" s="5">
@@ -7986,44 +7986,92 @@
         <v>6465.5982999999997</v>
       </c>
       <c r="F327" s="5">
-        <v>149525707100</v>
+        <v>149525707198</v>
       </c>
       <c r="G327" s="5"/>
     </row>
     <row r="328" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A328" s="1"/>
-      <c r="B328" s="5"/>
-      <c r="C328" s="5"/>
-      <c r="D328" s="5"/>
-      <c r="E328" s="5"/>
-      <c r="F328" s="5"/>
+      <c r="A328" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B328" s="5">
+        <v>6489.8586999999998</v>
+      </c>
+      <c r="C328" s="5">
+        <v>6534.0841</v>
+      </c>
+      <c r="D328" s="5">
+        <v>6470.9929000000002</v>
+      </c>
+      <c r="E328" s="5">
+        <v>6533.3261000000002</v>
+      </c>
+      <c r="F328" s="5">
+        <v>149939547866</v>
+      </c>
       <c r="G328" s="5"/>
     </row>
     <row r="329" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A329" s="1"/>
-      <c r="B329" s="5"/>
-      <c r="C329" s="5"/>
-      <c r="D329" s="5"/>
-      <c r="E329" s="5"/>
-      <c r="F329" s="5"/>
+      <c r="A329" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B329" s="5">
+        <v>6495.2488000000003</v>
+      </c>
+      <c r="C329" s="5">
+        <v>6540.5316000000003</v>
+      </c>
+      <c r="D329" s="5">
+        <v>6487.6113999999998</v>
+      </c>
+      <c r="E329" s="5">
+        <v>6532.3441999999995</v>
+      </c>
+      <c r="F329" s="5">
+        <v>149020189352</v>
+      </c>
       <c r="G329" s="5"/>
     </row>
     <row r="330" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A330" s="1"/>
-      <c r="B330" s="5"/>
-      <c r="C330" s="5"/>
-      <c r="D330" s="5"/>
-      <c r="E330" s="5"/>
-      <c r="F330" s="5"/>
+      <c r="A330" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B330" s="5">
+        <v>6579.6706000000004</v>
+      </c>
+      <c r="C330" s="5">
+        <v>6639.6414999999997</v>
+      </c>
+      <c r="D330" s="5">
+        <v>6555.5717000000004</v>
+      </c>
+      <c r="E330" s="5">
+        <v>6633.4826000000003</v>
+      </c>
+      <c r="F330" s="5">
+        <v>160585594481</v>
+      </c>
       <c r="G330" s="5"/>
     </row>
     <row r="331" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A331" s="1"/>
-      <c r="B331" s="5"/>
-      <c r="C331" s="5"/>
-      <c r="D331" s="5"/>
-      <c r="E331" s="5"/>
-      <c r="F331" s="5"/>
+      <c r="A331" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B331" s="5">
+        <v>6645.7847000000002</v>
+      </c>
+      <c r="C331" s="5">
+        <v>6645.7847000000002</v>
+      </c>
+      <c r="D331" s="5">
+        <v>6568.9422999999997</v>
+      </c>
+      <c r="E331" s="5">
+        <v>6605.7222000000002</v>
+      </c>
+      <c r="F331" s="5">
+        <v>149929765083</v>
+      </c>
       <c r="G331" s="5"/>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\gx_pit_mom_Auto_Bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EE44C23-87BB-4A54-899C-F85B67989259}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92BCEA2E-C8C4-42E9-B2AF-02D7DA3D601C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -649,7 +649,7 @@
         <v>45659</v>
       </c>
       <c r="B7" s="5">
-        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=325")</f>
+        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=327")</f>
         <v>4744.6453000000001</v>
       </c>
       <c r="C7" s="5">
@@ -8075,21 +8075,45 @@
       <c r="G331" s="5"/>
     </row>
     <row r="332" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A332" s="1"/>
-      <c r="B332" s="5"/>
-      <c r="C332" s="5"/>
-      <c r="D332" s="5"/>
-      <c r="E332" s="5"/>
-      <c r="F332" s="5"/>
+      <c r="A332" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B332" s="5">
+        <v>6567.4485000000004</v>
+      </c>
+      <c r="C332" s="5">
+        <v>6689.7367999999997</v>
+      </c>
+      <c r="D332" s="5">
+        <v>6567.4485000000004</v>
+      </c>
+      <c r="E332" s="5">
+        <v>6686.8649999999998</v>
+      </c>
+      <c r="F332" s="5">
+        <v>146139793360</v>
+      </c>
       <c r="G332" s="5"/>
     </row>
     <row r="333" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A333" s="1"/>
-      <c r="B333" s="5"/>
-      <c r="C333" s="5"/>
-      <c r="D333" s="5"/>
-      <c r="E333" s="5"/>
-      <c r="F333" s="5"/>
+      <c r="A333" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B333" s="5">
+        <v>6718.1936999999998</v>
+      </c>
+      <c r="C333" s="5">
+        <v>6720.9431999999997</v>
+      </c>
+      <c r="D333" s="5">
+        <v>6552.9453000000003</v>
+      </c>
+      <c r="E333" s="5">
+        <v>6552.9453000000003</v>
+      </c>
+      <c r="F333" s="5">
+        <v>157163304853</v>
+      </c>
       <c r="G333" s="5"/>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\gx_pit_mom_Auto_Bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92BCEA2E-C8C4-42E9-B2AF-02D7DA3D601C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D48443-6A84-4883-8CB0-F8B2FE244F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -649,7 +649,7 @@
         <v>45659</v>
       </c>
       <c r="B7" s="5">
-        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=327")</f>
+        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=328")</f>
         <v>4744.6453000000001</v>
       </c>
       <c r="C7" s="5">
@@ -8117,12 +8117,24 @@
       <c r="G333" s="5"/>
     </row>
     <row r="334" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A334" s="1"/>
-      <c r="B334" s="5"/>
-      <c r="C334" s="5"/>
-      <c r="D334" s="5"/>
-      <c r="E334" s="5"/>
-      <c r="F334" s="5"/>
+      <c r="A334" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B334" s="5">
+        <v>6552.6876000000002</v>
+      </c>
+      <c r="C334" s="5">
+        <v>6592.2083000000002</v>
+      </c>
+      <c r="D334" s="5">
+        <v>6438.1360000000004</v>
+      </c>
+      <c r="E334" s="5">
+        <v>6481.3375999999998</v>
+      </c>
+      <c r="F334" s="5">
+        <v>151869598900</v>
+      </c>
       <c r="G334" s="5"/>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\gx_pit_mom_Auto_Bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D48443-6A84-4883-8CB0-F8B2FE244F95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71F95087-D185-4ED7-A6E4-7A17D35E6A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -649,7 +649,7 @@
         <v>45659</v>
       </c>
       <c r="B7" s="5">
-        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=328")</f>
+        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=329")</f>
         <v>4744.6453000000001</v>
       </c>
       <c r="C7" s="5">
@@ -8133,17 +8133,29 @@
         <v>6481.3375999999998</v>
       </c>
       <c r="F334" s="5">
-        <v>151869598900</v>
+        <v>151869598940</v>
       </c>
       <c r="G334" s="5"/>
     </row>
     <row r="335" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A335" s="1"/>
-      <c r="B335" s="5"/>
-      <c r="C335" s="5"/>
-      <c r="D335" s="5"/>
-      <c r="E335" s="5"/>
-      <c r="F335" s="5"/>
+      <c r="A335" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B335" s="5">
+        <v>6452.1196</v>
+      </c>
+      <c r="C335" s="5">
+        <v>6515.5868</v>
+      </c>
+      <c r="D335" s="5">
+        <v>6433.2421999999997</v>
+      </c>
+      <c r="E335" s="5">
+        <v>6477.2115000000003</v>
+      </c>
+      <c r="F335" s="5">
+        <v>130616338400</v>
+      </c>
       <c r="G335" s="5"/>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\gx_pit_mom_Auto_Bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71F95087-D185-4ED7-A6E4-7A17D35E6A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ACACAD2-200E-4DFC-A192-5D126B2E4EE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -649,7 +649,7 @@
         <v>45659</v>
       </c>
       <c r="B7" s="5">
-        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=329")</f>
+        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=331")</f>
         <v>4744.6453000000001</v>
       </c>
       <c r="C7" s="5">
@@ -8154,26 +8154,50 @@
         <v>6477.2115000000003</v>
       </c>
       <c r="F335" s="5">
-        <v>130616338400</v>
+        <v>130616338408.99998</v>
       </c>
       <c r="G335" s="5"/>
     </row>
     <row r="336" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A336" s="1"/>
-      <c r="B336" s="5"/>
-      <c r="C336" s="5"/>
-      <c r="D336" s="5"/>
-      <c r="E336" s="5"/>
-      <c r="F336" s="5"/>
+      <c r="A336" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B336" s="5">
+        <v>6458.9701999999997</v>
+      </c>
+      <c r="C336" s="5">
+        <v>6527.5784999999996</v>
+      </c>
+      <c r="D336" s="5">
+        <v>6399.2741999999998</v>
+      </c>
+      <c r="E336" s="5">
+        <v>6526.0258000000003</v>
+      </c>
+      <c r="F336" s="5">
+        <v>129356062061.99998</v>
+      </c>
       <c r="G336" s="5"/>
     </row>
     <row r="337" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A337" s="1"/>
-      <c r="B337" s="5"/>
-      <c r="C337" s="5"/>
-      <c r="D337" s="5"/>
-      <c r="E337" s="5"/>
-      <c r="F337" s="5"/>
+      <c r="A337" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B337" s="5">
+        <v>6494.7687999999998</v>
+      </c>
+      <c r="C337" s="5">
+        <v>6538.0591000000004</v>
+      </c>
+      <c r="D337" s="5">
+        <v>6472.8267999999998</v>
+      </c>
+      <c r="E337" s="5">
+        <v>6525.0582999999997</v>
+      </c>
+      <c r="F337" s="5">
+        <v>127839466100</v>
+      </c>
       <c r="G337" s="5"/>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\gx_pit_mom_Auto_Bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ACACAD2-200E-4DFC-A192-5D126B2E4EE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26F91381-B712-45FB-AADC-04E2C1E2CFA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -649,7 +649,7 @@
         <v>45659</v>
       </c>
       <c r="B7" s="5">
-        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=331")</f>
+        <f>[1]!WSD(B3,B6:F6,B1,B2,"TradingCalendar=SSE","PriceAdj=F","rptType=1","Version=1","ShowParams=Y","cols=5;rows=332")</f>
         <v>4744.6453000000001</v>
       </c>
       <c r="C7" s="5">
@@ -8196,17 +8196,29 @@
         <v>6525.0582999999997</v>
       </c>
       <c r="F337" s="5">
-        <v>127839466100</v>
+        <v>127839466151</v>
       </c>
       <c r="G337" s="5"/>
     </row>
     <row r="338" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A338" s="1"/>
-      <c r="B338" s="5"/>
-      <c r="C338" s="5"/>
-      <c r="D338" s="5"/>
-      <c r="E338" s="5"/>
-      <c r="F338" s="5"/>
+      <c r="A338" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B338" s="5">
+        <v>6563.1629000000003</v>
+      </c>
+      <c r="C338" s="5">
+        <v>6616.3422</v>
+      </c>
+      <c r="D338" s="5">
+        <v>6361.9348</v>
+      </c>
+      <c r="E338" s="5">
+        <v>6368.4413999999997</v>
+      </c>
+      <c r="F338" s="5">
+        <v>153747885000</v>
+      </c>
       <c r="G338" s="5"/>
     </row>
     <row r="339" spans="1:7" x14ac:dyDescent="0.25">

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2292"/>
+  <dimension ref="A1:G2293"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53216,6 +53216,29 @@
       </c>
       <c r="G2292" t="inlineStr"/>
     </row>
+    <row r="2293">
+      <c r="A2293" t="inlineStr">
+        <is>
+          <t>2026-06-08</t>
+        </is>
+      </c>
+      <c r="B2293" t="n">
+        <v>6113.17</v>
+      </c>
+      <c r="C2293" t="n">
+        <v>6232.53</v>
+      </c>
+      <c r="D2293" t="n">
+        <v>6061.39</v>
+      </c>
+      <c r="E2293" t="n">
+        <v>6119.24</v>
+      </c>
+      <c r="F2293" t="n">
+        <v>1397132253</v>
+      </c>
+      <c r="G2293" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2293"/>
+  <dimension ref="A1:G2294"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53239,6 +53239,29 @@
       </c>
       <c r="G2293" t="inlineStr"/>
     </row>
+    <row r="2294">
+      <c r="A2294" t="inlineStr">
+        <is>
+          <t>2026-06-09</t>
+        </is>
+      </c>
+      <c r="B2294" t="n">
+        <v>6176.86</v>
+      </c>
+      <c r="C2294" t="n">
+        <v>6255.62</v>
+      </c>
+      <c r="D2294" t="n">
+        <v>6125.51</v>
+      </c>
+      <c r="E2294" t="n">
+        <v>6254.74</v>
+      </c>
+      <c r="F2294" t="n">
+        <v>1251124002</v>
+      </c>
+      <c r="G2294" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2297"/>
+  <dimension ref="A1:G2298"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53331,6 +53331,29 @@
       </c>
       <c r="G2297" t="inlineStr"/>
     </row>
+    <row r="2298">
+      <c r="A2298" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="B2298" t="n">
+        <v>6254.44</v>
+      </c>
+      <c r="C2298" t="n">
+        <v>6380.65</v>
+      </c>
+      <c r="D2298" t="n">
+        <v>6246.26</v>
+      </c>
+      <c r="E2298" t="n">
+        <v>6380.16</v>
+      </c>
+      <c r="F2298" t="n">
+        <v>1399464054</v>
+      </c>
+      <c r="G2298" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2299"/>
+  <dimension ref="A1:G2300"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53377,6 +53377,29 @@
       </c>
       <c r="G2299" t="inlineStr"/>
     </row>
+    <row r="2300">
+      <c r="A2300" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="B2300" t="n">
+        <v>6383.6</v>
+      </c>
+      <c r="C2300" t="n">
+        <v>6479.2</v>
+      </c>
+      <c r="D2300" t="n">
+        <v>6383.56</v>
+      </c>
+      <c r="E2300" t="n">
+        <v>6477.07</v>
+      </c>
+      <c r="F2300" t="n">
+        <v>1313683477</v>
+      </c>
+      <c r="G2300" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2300"/>
+  <dimension ref="A1:G2301"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53400,6 +53400,29 @@
       </c>
       <c r="G2300" t="inlineStr"/>
     </row>
+    <row r="2301">
+      <c r="A2301" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="B2301" t="n">
+        <v>6453.66</v>
+      </c>
+      <c r="C2301" t="n">
+        <v>6526.32</v>
+      </c>
+      <c r="D2301" t="n">
+        <v>6453.35</v>
+      </c>
+      <c r="E2301" t="n">
+        <v>6499.33</v>
+      </c>
+      <c r="F2301" t="n">
+        <v>1380767454</v>
+      </c>
+      <c r="G2301" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2303"/>
+  <dimension ref="A1:G2304"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58063,6 +58063,31 @@
         <v>3392445051047</v>
       </c>
     </row>
+    <row r="2304">
+      <c r="A2304" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="B2304" t="n">
+        <v>6453.7</v>
+      </c>
+      <c r="C2304" t="n">
+        <v>6536.92</v>
+      </c>
+      <c r="D2304" t="n">
+        <v>6432.87</v>
+      </c>
+      <c r="E2304" t="n">
+        <v>6531.25</v>
+      </c>
+      <c r="F2304" t="n">
+        <v>1391459779</v>
+      </c>
+      <c r="G2304" t="n">
+        <v>3225742626769</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2304"/>
+  <dimension ref="A1:G2305"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53492,6 +53492,29 @@
       </c>
       <c r="G2304" t="inlineStr"/>
     </row>
+    <row r="2305">
+      <c r="A2305" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="B2305" t="n">
+        <v>6538.69</v>
+      </c>
+      <c r="C2305" t="n">
+        <v>6591.08</v>
+      </c>
+      <c r="D2305" t="n">
+        <v>6519.12</v>
+      </c>
+      <c r="E2305" t="n">
+        <v>6586.23</v>
+      </c>
+      <c r="F2305" t="n">
+        <v>1457211179</v>
+      </c>
+      <c r="G2305" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2306"/>
+  <dimension ref="A1:G2307"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58138,6 +58138,31 @@
         <v>3481986770996</v>
       </c>
     </row>
+    <row r="2307">
+      <c r="A2307" t="inlineStr">
+        <is>
+          <t>2026-06-29</t>
+        </is>
+      </c>
+      <c r="B2307" t="n">
+        <v>6404.3</v>
+      </c>
+      <c r="C2307" t="n">
+        <v>6445.64</v>
+      </c>
+      <c r="D2307" t="n">
+        <v>6310.39</v>
+      </c>
+      <c r="E2307" t="n">
+        <v>6443.3</v>
+      </c>
+      <c r="F2307" t="n">
+        <v>1423844236</v>
+      </c>
+      <c r="G2307" t="n">
+        <v>3452724551942</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2307"/>
+  <dimension ref="A1:G2308"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58163,6 +58163,31 @@
         <v>3452724551942</v>
       </c>
     </row>
+    <row r="2308">
+      <c r="A2308" t="inlineStr">
+        <is>
+          <t>2026-06-30</t>
+        </is>
+      </c>
+      <c r="B2308" t="n">
+        <v>6429.16</v>
+      </c>
+      <c r="C2308" t="n">
+        <v>6558.04</v>
+      </c>
+      <c r="D2308" t="n">
+        <v>6424.59</v>
+      </c>
+      <c r="E2308" t="n">
+        <v>6551.62</v>
+      </c>
+      <c r="F2308" t="n">
+        <v>1300395371</v>
+      </c>
+      <c r="G2308" t="n">
+        <v>3207382923774</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2309"/>
+  <dimension ref="A1:G2310"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58213,6 +58213,31 @@
         <v>3587114494786</v>
       </c>
     </row>
+    <row r="2310">
+      <c r="A2310" t="inlineStr">
+        <is>
+          <t>2026-07-02</t>
+        </is>
+      </c>
+      <c r="B2310" t="n">
+        <v>6437.21</v>
+      </c>
+      <c r="C2310" t="n">
+        <v>6517.42</v>
+      </c>
+      <c r="D2310" t="n">
+        <v>6359.07</v>
+      </c>
+      <c r="E2310" t="n">
+        <v>6376.36</v>
+      </c>
+      <c r="F2310" t="n">
+        <v>1462989352</v>
+      </c>
+      <c r="G2310" t="n">
+        <v>3368859994111</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2311"/>
+  <dimension ref="A1:G2312"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58263,6 +58263,31 @@
         <v>3119008304759</v>
       </c>
     </row>
+    <row r="2312">
+      <c r="A2312" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="B2312" t="n">
+        <v>6436.27</v>
+      </c>
+      <c r="C2312" t="n">
+        <v>6450.18</v>
+      </c>
+      <c r="D2312" t="n">
+        <v>6300.07</v>
+      </c>
+      <c r="E2312" t="n">
+        <v>6350.89</v>
+      </c>
+      <c r="F2312" t="n">
+        <v>1298069835</v>
+      </c>
+      <c r="G2312" t="n">
+        <v>3019707852846</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2312"/>
+  <dimension ref="A1:G2313"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58288,6 +58288,31 @@
         <v>3019707852846</v>
       </c>
     </row>
+    <row r="2313">
+      <c r="A2313" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B2313" t="n">
+        <v>6317.01</v>
+      </c>
+      <c r="C2313" t="n">
+        <v>6350.87</v>
+      </c>
+      <c r="D2313" t="n">
+        <v>6209.88</v>
+      </c>
+      <c r="E2313" t="n">
+        <v>6246.03</v>
+      </c>
+      <c r="F2313" t="n">
+        <v>1134990758</v>
+      </c>
+      <c r="G2313" t="n">
+        <v>2518713551245</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2314"/>
+  <dimension ref="A1:G2315"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53722,6 +53722,29 @@
       </c>
       <c r="G2314" t="inlineStr"/>
     </row>
+    <row r="2315">
+      <c r="A2315" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B2315" t="n">
+        <v>6182.77</v>
+      </c>
+      <c r="C2315" t="n">
+        <v>6311.8</v>
+      </c>
+      <c r="D2315" t="n">
+        <v>6086.1</v>
+      </c>
+      <c r="E2315" t="n">
+        <v>6304.43</v>
+      </c>
+      <c r="F2315" t="n">
+        <v>1207602537</v>
+      </c>
+      <c r="G2315" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2316"/>
+  <dimension ref="A1:G2317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53768,6 +53768,29 @@
       </c>
       <c r="G2316" t="inlineStr"/>
     </row>
+    <row r="2317">
+      <c r="A2317" t="inlineStr">
+        <is>
+          <t>2026-07-13</t>
+        </is>
+      </c>
+      <c r="B2317" t="n">
+        <v>6162.54</v>
+      </c>
+      <c r="C2317" t="n">
+        <v>6190.17</v>
+      </c>
+      <c r="D2317" t="n">
+        <v>5976.21</v>
+      </c>
+      <c r="E2317" t="n">
+        <v>6001.65</v>
+      </c>
+      <c r="F2317" t="n">
+        <v>1270613463</v>
+      </c>
+      <c r="G2317" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2317"/>
+  <dimension ref="A1:G2318"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58413,6 +58413,31 @@
         <v>2749648243827</v>
       </c>
     </row>
+    <row r="2318">
+      <c r="A2318" t="inlineStr">
+        <is>
+          <t>2026-07-14</t>
+        </is>
+      </c>
+      <c r="B2318" t="n">
+        <v>5999.02</v>
+      </c>
+      <c r="C2318" t="n">
+        <v>6119.19</v>
+      </c>
+      <c r="D2318" t="n">
+        <v>5913.58</v>
+      </c>
+      <c r="E2318" t="n">
+        <v>6119.19</v>
+      </c>
+      <c r="F2318" t="n">
+        <v>1203691448</v>
+      </c>
+      <c r="G2318" t="n">
+        <v>2646241081521</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2319"/>
+  <dimension ref="A1:G2320"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58463,6 +58463,31 @@
         <v>2518690994686</v>
       </c>
     </row>
+    <row r="2320">
+      <c r="A2320" t="inlineStr">
+        <is>
+          <t>2026-07-16</t>
+        </is>
+      </c>
+      <c r="B2320" t="n">
+        <v>5984.53</v>
+      </c>
+      <c r="C2320" t="n">
+        <v>6071.94</v>
+      </c>
+      <c r="D2320" t="n">
+        <v>5925.13</v>
+      </c>
+      <c r="E2320" t="n">
+        <v>5956.5</v>
+      </c>
+      <c r="F2320" t="n">
+        <v>1151014655</v>
+      </c>
+      <c r="G2320" t="n">
+        <v>2356578399515</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2320"/>
+  <dimension ref="A1:G2321"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58488,6 +58488,31 @@
         <v>2356578399515</v>
       </c>
     </row>
+    <row r="2321">
+      <c r="A2321" t="inlineStr">
+        <is>
+          <t>2026-07-17</t>
+        </is>
+      </c>
+      <c r="B2321" t="n">
+        <v>5917.18</v>
+      </c>
+      <c r="C2321" t="n">
+        <v>5920.71</v>
+      </c>
+      <c r="D2321" t="n">
+        <v>5636.84</v>
+      </c>
+      <c r="E2321" t="n">
+        <v>5671.75</v>
+      </c>
+      <c r="F2321" t="n">
+        <v>1359555959</v>
+      </c>
+      <c r="G2321" t="n">
+        <v>2602175889503</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/000985_prices.xlsx
+++ b/data/000985_prices.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\gx_pit_mom_Auto_Bot\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06F272CE-DA5E-4931-93AB-58FF411B2C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DB7CDDC-0E9B-4828-AA40-9E54D6259A1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3420" yWindow="3420" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -198,16 +198,16 @@
     <xf numFmtId="176" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -542,7 +542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G2433"/>
+  <dimension ref="A1:G2436"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.36328125" bestFit="1" customWidth="1"/>
@@ -632,7 +632,7 @@
         <v>42570</v>
       </c>
       <c r="B7" s="7">
-        <f>[1]!WSD(B3,B6:G6,B1,B2,"unit=1","TradingCalendar=SSE","rptType=1","Version=1","ShowParams=Y","UnitMask=32","cols=6;rows=2427")</f>
+        <f>[1]!WSD(B3,B6:G6,B1,B2,"unit=1","TradingCalendar=SSE","rptType=1","Version=1","ShowParams=Y","UnitMask=32","cols=6;rows=2430")</f>
         <v>4799.9991</v>
       </c>
       <c r="C7" s="7">
@@ -56447,6 +56447,75 @@
       </c>
       <c r="G2433" s="7">
         <v>2602175889503</v>
+      </c>
+    </row>
+    <row r="2434" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2434" s="1">
+        <v>46223</v>
+      </c>
+      <c r="B2434" s="7">
+        <v>5731.2191000000003</v>
+      </c>
+      <c r="C2434" s="7">
+        <v>5772.2106999999996</v>
+      </c>
+      <c r="D2434" s="7">
+        <v>5539.0392000000002</v>
+      </c>
+      <c r="E2434" s="7">
+        <v>5638.6185999999998</v>
+      </c>
+      <c r="F2434" s="7">
+        <v>142987607433</v>
+      </c>
+      <c r="G2434" s="7">
+        <v>2650229559275</v>
+      </c>
+    </row>
+    <row r="2435" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2435" s="1">
+        <v>46224</v>
+      </c>
+      <c r="B2435" s="7">
+        <v>5663.8751000000002</v>
+      </c>
+      <c r="C2435" s="7">
+        <v>5834.1704</v>
+      </c>
+      <c r="D2435" s="7">
+        <v>5510.4002</v>
+      </c>
+      <c r="E2435" s="7">
+        <v>5833.7268000000004</v>
+      </c>
+      <c r="F2435" s="7">
+        <v>151541877453</v>
+      </c>
+      <c r="G2435" s="7">
+        <v>2901920156472</v>
+      </c>
+    </row>
+    <row r="2436" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2436" s="1">
+        <v>46225</v>
+      </c>
+      <c r="B2436" s="7">
+        <v>5792.4529000000002</v>
+      </c>
+      <c r="C2436" s="7">
+        <v>5871.8368</v>
+      </c>
+      <c r="D2436" s="7">
+        <v>5757.7520000000004</v>
+      </c>
+      <c r="E2436" s="7">
+        <v>5790.7622000000001</v>
+      </c>
+      <c r="F2436" s="7">
+        <v>125478979400</v>
+      </c>
+      <c r="G2436" s="7">
+        <v>2602930506546</v>
       </c>
     </row>
   </sheetData>
